--- a/output/Jiangsu/泰州市_api_news.xlsx
+++ b/output/Jiangsu/泰州市_api_news.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="225">
   <si>
     <t>location</t>
   </si>
@@ -101,6 +101,9 @@
     <t>无条件</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>True</t>
   </si>
   <si>
@@ -110,9 +113,6 @@
     <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=1</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>泰州通信息数据分页查询</t>
   </si>
   <si>
@@ -122,427 +122,565 @@
     <t>2022-11-14</t>
   </si>
   <si>
+    <t>报废汽车回收拆解企业名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>工业农业</t>
+  </si>
+  <si>
+    <t>描述：报废汽车回收拆解企业名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市商务局</t>
+  </si>
+  <si>
+    <t>2022-12-12</t>
+  </si>
+  <si>
+    <t>2023-08-06</t>
+  </si>
+  <si>
+    <t>装备制造业重点领域首台（套）产品名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>安全生产</t>
+  </si>
+  <si>
+    <t>描述：装备制造业重点领域首台（套）产品名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市工业和信息化局</t>
+  </si>
+  <si>
+    <t>泰州市2022年高中阶段教师资格认定有条件通过人员名单数据量查询接口</t>
+  </si>
+  <si>
+    <t>教育文化</t>
+  </si>
+  <si>
+    <t>描述：泰州市2022年高中阶段教师资格认定有条件通过人员名单数据量查询接口</t>
+  </si>
+  <si>
+    <t>泰州市教育局</t>
+  </si>
+  <si>
+    <t>降雨量等级划分标准（毫米）数据量查询服务</t>
+  </si>
+  <si>
+    <t>气象服务</t>
+  </si>
+  <si>
+    <t>描述：降雨量等级划分标准（毫米）数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市气象局</t>
+  </si>
+  <si>
+    <t>院士工作站数据量查询服务</t>
+  </si>
+  <si>
+    <t>资源能源</t>
+  </si>
+  <si>
+    <t>描述：院士工作站数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市科学技术局</t>
+  </si>
+  <si>
+    <t>科技类民办非企业信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：科技类民办非企业信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>全市列入工信部准入名单的再生资源利用企业名单数据量查询接口</t>
+  </si>
+  <si>
+    <t>市场监管</t>
+  </si>
+  <si>
+    <t>描述：全市列入工信部准入名单的再生资源利用企业名单数据量查询接口</t>
+  </si>
+  <si>
+    <t>救助站管理机构数据量查询服务</t>
+  </si>
+  <si>
+    <t>社保就业</t>
+  </si>
+  <si>
+    <t>描述：救助站管理机构数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市民政局</t>
+  </si>
+  <si>
+    <t>2019年泰州市普通高中招生计划增加情况数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：2019年泰州市普通高中招生计划增加情况数据量查询服务</t>
+  </si>
+  <si>
+    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=2</t>
+  </si>
+  <si>
+    <t>游泳场所水质抽检结果公示信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>医疗卫生</t>
+  </si>
+  <si>
+    <t>描述：游泳场所水质抽检结果公示信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市卫生健康委员会</t>
+  </si>
+  <si>
+    <t>预防接种点信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：预防接种点信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市2022年高中阶段教师资格第二次认定通过人员名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：泰州市2022年高中阶段教师资格第二次认定通过人员名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>部门机构职能信息数据量查询接口</t>
+  </si>
+  <si>
+    <t>描述：部门机构职能信息数据量查询接口</t>
+  </si>
+  <si>
+    <t>市直学校卫生综合评价结果名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：市直学校卫生综合评价结果名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>防雷安全重点单位监管情况数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：防雷安全重点单位监管情况数据量查询服务</t>
+  </si>
+  <si>
+    <t>岗位责任人信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：岗位责任人信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>收支预算数信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：收支预算数信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>省级创新型领军企业信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：省级创新型领军企业信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>中小企业公共服务平台认定名单数据量查询接口</t>
+  </si>
+  <si>
+    <t>描述：中小企业公共服务平台认定名单数据量查询接口</t>
+  </si>
+  <si>
+    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=3</t>
+  </si>
+  <si>
+    <t>血站AED网点数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：血站AED网点数据量查询服务</t>
+  </si>
+  <si>
+    <t>省服务型制造示范（培育）企业名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：省服务型制造示范（培育）企业名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>报废车拆解资质企业信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：报废车拆解资质企业信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>制造业单项冠军示范企业（产品）名称数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：制造业单项冠军示范企业（产品）名称数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市第七批教坛新秀数据量查询接口</t>
+  </si>
+  <si>
+    <t>描述：泰州市第七批教坛新秀数据量查询接口</t>
+  </si>
+  <si>
+    <t>采供血机构数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：采供血机构数据量查询服务</t>
+  </si>
+  <si>
+    <t>中医临床人才名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：中医临床人才名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市科技专员列表数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：泰州市科技专员列表数据量查询服务</t>
+  </si>
+  <si>
+    <t>职业病鉴定办事机构数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：职业病鉴定办事机构数据量查询服务</t>
+  </si>
+  <si>
     <t>会计师事务所信息数据量查询服务</t>
   </si>
   <si>
-    <t>市场监管</t>
-  </si>
-  <si>
     <t>描述：会计师事务所信息数据量查询服务</t>
   </si>
   <si>
     <t>泰州市财政局</t>
   </si>
   <si>
-    <t>2022-12-12</t>
-  </si>
-  <si>
-    <t>2023-08-06</t>
-  </si>
-  <si>
-    <t>职业病鉴定办事机构数据量查询服务</t>
-  </si>
-  <si>
-    <t>医疗卫生</t>
-  </si>
-  <si>
-    <t>描述：职业病鉴定办事机构数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市卫生健康委员会</t>
-  </si>
-  <si>
-    <t>泰州市科技专员列表数据量查询服务</t>
-  </si>
-  <si>
-    <t>资源能源</t>
-  </si>
-  <si>
-    <t>描述：泰州市科技专员列表数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市科学技术局</t>
-  </si>
-  <si>
-    <t>中医临床人才名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：中医临床人才名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>报废车拆解资质企业信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：报废车拆解资质企业信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市商务局</t>
-  </si>
-  <si>
-    <t>采供血机构数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：采供血机构数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市第七批教坛新秀数据量查询接口</t>
-  </si>
-  <si>
-    <t>教育文化</t>
-  </si>
-  <si>
-    <t>描述：泰州市第七批教坛新秀数据量查询接口</t>
-  </si>
-  <si>
-    <t>泰州市教育局</t>
-  </si>
-  <si>
-    <t>制造业单项冠军示范企业（产品）名称数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：制造业单项冠军示范企业（产品）名称数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市工业和信息化局</t>
-  </si>
-  <si>
-    <t>救助站管理机构数据量查询服务</t>
-  </si>
-  <si>
-    <t>社保就业</t>
-  </si>
-  <si>
-    <t>描述：救助站管理机构数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市民政局</t>
-  </si>
-  <si>
-    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=2</t>
-  </si>
-  <si>
-    <t>血站AED网点数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：血站AED网点数据量查询服务</t>
-  </si>
-  <si>
-    <t>省服务型制造示范（培育）企业名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：省服务型制造示范（培育）企业名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>省级创新型领军企业信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：省级创新型领军企业信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>中小企业公共服务平台认定名单数据量查询接口</t>
-  </si>
-  <si>
-    <t>描述：中小企业公共服务平台认定名单数据量查询接口</t>
-  </si>
-  <si>
-    <t>岗位责任人信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：岗位责任人信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>收支预算数信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>安全生产</t>
-  </si>
-  <si>
-    <t>描述：收支预算数信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>防雷安全重点单位监管情况数据量查询服务</t>
-  </si>
-  <si>
-    <t>气象服务</t>
-  </si>
-  <si>
-    <t>描述：防雷安全重点单位监管情况数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市气象局</t>
-  </si>
-  <si>
-    <t>市直学校卫生综合评价结果名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：市直学校卫生综合评价结果名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>2019年泰州市普通高中招生计划增加情况数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：2019年泰州市普通高中招生计划增加情况数据量查询服务</t>
-  </si>
-  <si>
-    <t>部门机构职能信息数据量查询接口</t>
-  </si>
-  <si>
-    <t>描述：部门机构职能信息数据量查询接口</t>
-  </si>
-  <si>
-    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=3</t>
-  </si>
-  <si>
-    <t>泰州市2022年高中阶段教师资格第二次认定通过人员名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：泰州市2022年高中阶段教师资格第二次认定通过人员名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>预防接种点信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：预防接种点信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>游泳场所水质抽检结果公示信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：游泳场所水质抽检结果公示信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>全市列入工信部准入名单的再生资源利用企业名单数据量查询接口</t>
-  </si>
-  <si>
-    <t>描述：全市列入工信部准入名单的再生资源利用企业名单数据量查询接口</t>
-  </si>
-  <si>
-    <t>科技类民办非企业信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：科技类民办非企业信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>院士工作站数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：院士工作站数据量查询服务</t>
-  </si>
-  <si>
-    <t>降雨量等级划分标准（毫米）数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：降雨量等级划分标准（毫米）数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市2022年高中阶段教师资格认定有条件通过人员名单数据量查询接口</t>
-  </si>
-  <si>
-    <t>描述：泰州市2022年高中阶段教师资格认定有条件通过人员名单数据量查询接口</t>
-  </si>
-  <si>
-    <t>装备制造业重点领域首台（套）产品名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：装备制造业重点领域首台（套）产品名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>报废汽车回收拆解企业名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>工业农业</t>
-  </si>
-  <si>
-    <t>描述：报废汽车回收拆解企业名录数据量查询服务</t>
-  </si>
-  <si>
     <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=4</t>
   </si>
   <si>
+    <t>小微企业创业创新示范基地认定名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：小微企业创业创新示范基地认定名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>经营性公墓名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：经营性公墓名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>实际利用外资数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：实际利用外资数据量查询服务</t>
+  </si>
+  <si>
+    <t>消毒产品生产企业监督检查情况汇总表数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：消毒产品生产企业监督检查情况汇总表数据量查询服务</t>
+  </si>
+  <si>
+    <t>医学新技术引进奖名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：医学新技术引进奖名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>优秀戎耀之家名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：优秀戎耀之家名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市退役军人事务局</t>
+  </si>
+  <si>
+    <t>JKM扫码核验（限泰州地区使用）</t>
+  </si>
+  <si>
+    <t>描述：JKM扫码核验（限泰州地区使用）</t>
+  </si>
+  <si>
+    <t>2022-10-24</t>
+  </si>
+  <si>
+    <t>有条件</t>
+  </si>
+  <si>
+    <t>中心血站采血站（点）信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：中心血站采血站（点）信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>一类疫苗接种公示（免费接种）数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：一类疫苗接种公示（免费接种）数据量查询服务</t>
+  </si>
+  <si>
+    <t>各市（区）中考报名咨询电话数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：各市（区）中考报名咨询电话数据量查询服务</t>
+  </si>
+  <si>
+    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=5</t>
+  </si>
+  <si>
+    <t>JKM根据身份证和姓名（限泰州地区使用）</t>
+  </si>
+  <si>
+    <t>描述：JKM根据身份证和姓名（限泰州地区使用）</t>
+  </si>
+  <si>
+    <t>殡仪服务机构名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：殡仪服务机构名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>储血点及其供血医院名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：储血点及其供血医院名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>公共场所卫生信誉度信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：公共场所卫生信誉度信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>升放气球活动许可信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：升放气球活动许可信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>卫健委数据目录（血站）数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：卫健委数据目录（血站）数据量查询服务</t>
+  </si>
+  <si>
+    <t>全市残疾人托养数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：全市残疾人托养数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市残疾人联合会</t>
+  </si>
+  <si>
+    <t>泰州市医学重点学科名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：泰州市医学重点学科名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>狂犬病暴露处置门诊名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：狂犬病暴露处置门诊名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市2022年高中阶段教师资格认定通过人员名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：泰州市2022年高中阶段教师资格认定通过人员名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=6</t>
+  </si>
+  <si>
+    <t>技术合同认定情况数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：技术合同认定情况数据量查询服务</t>
+  </si>
+  <si>
+    <t>国家卫生城镇名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：国家卫生城镇名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>财政拨款支出预算信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：财政拨款支出预算信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>成品油零售企业信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：成品油零售企业信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>血站服务网点数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：血站服务网点数据量查询服务</t>
+  </si>
+  <si>
+    <t>省级工业设计中心名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：省级工业设计中心名单数据量查询服务</t>
+  </si>
+  <si>
     <t>专精特新产品企业名称数据量查询服务</t>
   </si>
   <si>
     <t>描述：专精特新产品企业名称数据量查询服务</t>
   </si>
   <si>
-    <t>省级工业设计中心名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：省级工业设计中心名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>血站服务网点数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：血站服务网点数据量查询服务</t>
-  </si>
-  <si>
-    <t>财政拨款支出预算信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：财政拨款支出预算信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>成品油零售企业信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：成品油零售企业信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>各市（区）中考报名咨询电话数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：各市（区）中考报名咨询电话数据量查询服务</t>
-  </si>
-  <si>
-    <t>医学新技术引进奖名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：医学新技术引进奖名单数据量查询服务</t>
-  </si>
-  <si>
     <t>泰州市第七批教学能手数据量查询服务</t>
   </si>
   <si>
     <t>描述：泰州市第七批教学能手数据量查询服务</t>
   </si>
   <si>
-    <t>国家卫生城镇名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：国家卫生城镇名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>技术合同认定情况数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：技术合同认定情况数据量查询服务</t>
-  </si>
-  <si>
-    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=5</t>
-  </si>
-  <si>
-    <t>泰州市2022年高中阶段教师资格认定通过人员名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：泰州市2022年高中阶段教师资格认定通过人员名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>升放气球活动许可信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：升放气球活动许可信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>卫健委数据目录（血站）数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：卫健委数据目录（血站）数据量查询服务</t>
-  </si>
-  <si>
-    <t>全市残疾人托养数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：全市残疾人托养数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市残疾人联合会</t>
-  </si>
-  <si>
-    <t>有条件</t>
-  </si>
-  <si>
-    <t>泰州市医学重点学科名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：泰州市医学重点学科名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>狂犬病暴露处置门诊名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：狂犬病暴露处置门诊名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>公共场所卫生信誉度信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：公共场所卫生信誉度信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>储血点及其供血医院名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：储血点及其供血医院名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>殡仪服务机构名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：殡仪服务机构名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>JKM根据身份证和姓名（限泰州地区使用）</t>
-  </si>
-  <si>
-    <t>描述：JKM根据身份证和姓名（限泰州地区使用）</t>
-  </si>
-  <si>
-    <t>2022-10-24</t>
-  </si>
-  <si>
-    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=6</t>
-  </si>
-  <si>
-    <t>一类疫苗接种公示（免费接种）数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：一类疫苗接种公示（免费接种）数据量查询服务</t>
-  </si>
-  <si>
-    <t>中心血站采血站（点）信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：中心血站采血站（点）信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>JKM扫码核验（限泰州地区使用）</t>
-  </si>
-  <si>
-    <t>描述：JKM扫码核验（限泰州地区使用）</t>
-  </si>
-  <si>
-    <t>优秀戎耀之家名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：优秀戎耀之家名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市退役军人事务局</t>
-  </si>
-  <si>
-    <t>经营性公墓名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：经营性公墓名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>消毒产品生产企业监督检查情况汇总表数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：消毒产品生产企业监督检查情况汇总表数据量查询服务</t>
-  </si>
-  <si>
-    <t>小微企业创业创新示范基地认定名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：小微企业创业创新示范基地认定名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>实际利用外资数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：实际利用外资数据量查询服务</t>
+    <t>生活饮用水管网末稍水水质监测结果公示数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：生活饮用水管网末稍水水质监测结果公示数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市第七批市直级学科带头人数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：泰州市第七批市直级学科带头人数据量查询服务</t>
+  </si>
+  <si>
+    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=7</t>
+  </si>
+  <si>
+    <t>已备案单用途商业预付卡（规模发卡）企业名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>生态环境</t>
+  </si>
+  <si>
+    <t>描述：已备案单用途商业预付卡（规模发卡）企业名单数据量查询服务</t>
+  </si>
+  <si>
+    <t>国家企业重点实验室信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：国家企业重点实验室信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>急救中心信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：急救中心信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>成品油零售经营资格审批信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：成品油零售经营资格审批信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>外资企业年度年报信息(可向社会公示的部分)数据量查询服务</t>
+  </si>
+  <si>
+    <t>财税金融</t>
+  </si>
+  <si>
+    <t>描述：外资企业年度年报信息(可向社会公示的部分)数据量查询服务</t>
+  </si>
+  <si>
+    <t>防雷装置竣工验收意见书数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：防雷装置竣工验收意见书数据量查询服务</t>
+  </si>
+  <si>
+    <t>免费婚前医学检查机构信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：免费婚前医学检查机构信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>降雪量等级划分标准（毫米）数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：降雪量等级划分标准（毫米）数据量查询服务</t>
+  </si>
+  <si>
+    <t>完成市级淘汰落后（低端低效）产能任务企业名称数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：完成市级淘汰落后（低端低效）产能任务企业名称数据量查询服务</t>
+  </si>
+  <si>
+    <t>艾滋病自愿免费咨询检测点数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：艾滋病自愿免费咨询检测点数据量查询服务</t>
+  </si>
+  <si>
+    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=8</t>
+  </si>
+  <si>
+    <t>消毒产品生产企业名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：消毒产品生产企业名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>HIV抗体初筛实验室技术评估合格单位名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：HIV抗体初筛实验室技术评估合格单位名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>青年岗位操作能手数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：青年岗位操作能手数据量查询服务</t>
+  </si>
+  <si>
+    <t>江苏省重点培育和发展的国际知名品牌企业信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：江苏省重点培育和发展的国际知名品牌企业信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市核酸采样点基本信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：泰州市核酸采样点基本信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>泰州市第七批学科带头人数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：泰州市第七批学科带头人数据量查询服务</t>
+  </si>
+  <si>
+    <t>灾害性天气预警信号标准数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：灾害性天气预警信号标准数据量查询服务</t>
+  </si>
+  <si>
+    <t>健康三大指标统计信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：健康三大指标统计信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>餐饮具集中消毒服务机构名录数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：餐饮具集中消毒服务机构名录数据量查询服务</t>
   </si>
   <si>
     <t>残疾人专门协会名录数据量查询服务</t>
@@ -551,157 +689,19 @@
     <t>描述：残疾人专门协会名录数据量查询服务</t>
   </si>
   <si>
+    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=9</t>
+  </si>
+  <si>
+    <t>财政拨款三公经费决算信息数据量查询服务</t>
+  </si>
+  <si>
+    <t>描述：财政拨款三公经费决算信息数据量查询服务</t>
+  </si>
+  <si>
     <t>继续医学教育项目汇总信息数据量查询服务</t>
   </si>
   <si>
     <t>描述：继续医学教育项目汇总信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=7</t>
-  </si>
-  <si>
-    <t>财政拨款三公经费决算信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：财政拨款三公经费决算信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>餐饮具集中消毒服务机构名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：餐饮具集中消毒服务机构名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>健康三大指标统计信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：健康三大指标统计信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>灾害性天气预警信号标准数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：灾害性天气预警信号标准数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市第七批学科带头人数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：泰州市第七批学科带头人数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市核酸采样点基本信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：泰州市核酸采样点基本信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>江苏省重点培育和发展的国际知名品牌企业信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：江苏省重点培育和发展的国际知名品牌企业信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>青年岗位操作能手数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：青年岗位操作能手数据量查询服务</t>
-  </si>
-  <si>
-    <t>HIV抗体初筛实验室技术评估合格单位名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：HIV抗体初筛实验室技术评估合格单位名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>艾滋病自愿免费咨询检测点数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：艾滋病自愿免费咨询检测点数据量查询服务</t>
-  </si>
-  <si>
-    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=8</t>
-  </si>
-  <si>
-    <t>完成市级淘汰落后（低端低效）产能任务企业名称数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：完成市级淘汰落后（低端低效）产能任务企业名称数据量查询服务</t>
-  </si>
-  <si>
-    <t>降雪量等级划分标准（毫米）数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：降雪量等级划分标准（毫米）数据量查询服务</t>
-  </si>
-  <si>
-    <t>免费婚前医学检查机构信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：免费婚前医学检查机构信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>防雷装置竣工验收意见书数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：防雷装置竣工验收意见书数据量查询服务</t>
-  </si>
-  <si>
-    <t>外资企业年度年报信息(可向社会公示的部分)数据量查询服务</t>
-  </si>
-  <si>
-    <t>财税金融</t>
-  </si>
-  <si>
-    <t>描述：外资企业年度年报信息(可向社会公示的部分)数据量查询服务</t>
-  </si>
-  <si>
-    <t>成品油零售经营资格审批信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：成品油零售经营资格审批信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>急救中心信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：急救中心信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>国家企业重点实验室信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：国家企业重点实验室信息数据量查询服务</t>
-  </si>
-  <si>
-    <t>生活饮用水管网末稍水水质监测结果公示数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：生活饮用水管网末稍水水质监测结果公示数据量查询服务</t>
-  </si>
-  <si>
-    <t>消毒产品生产企业名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：消毒产品生产企业名录数据量查询服务</t>
-  </si>
-  <si>
-    <t>http://opendata.taizhou.gov.cn/oportal/api/index?page=9</t>
-  </si>
-  <si>
-    <t>已备案单用途商业预付卡（规模发卡）企业名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>生态环境</t>
-  </si>
-  <si>
-    <t>描述：已备案单用途商业预付卡（规模发卡）企业名单数据量查询服务</t>
-  </si>
-  <si>
-    <t>泰州市第七批市直级学科带头人数据量查询服务</t>
-  </si>
-  <si>
-    <t>描述：泰州市第七批市直级学科带头人数据量查询服务</t>
   </si>
 </sst>
 </file>
@@ -1773,29 +1773,29 @@
       <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="I2">
-        <v>0</v>
+      <c r="I2" t="s">
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2">
-        <v>19014</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
+        <v>19638</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1823,29 +1823,29 @@
       <c r="H3" t="s">
         <v>23</v>
       </c>
-      <c r="I3">
-        <v>0</v>
+      <c r="I3" t="s">
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>18212</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
+        <v>18825</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1873,29 +1873,29 @@
       <c r="H4" t="s">
         <v>23</v>
       </c>
-      <c r="I4">
-        <v>0</v>
+      <c r="I4" t="s">
+        <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L4">
-        <v>12438</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
+        <v>16700</v>
+      </c>
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" t="s">
+        <v>24</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1923,29 +1923,29 @@
       <c r="H5" t="s">
         <v>23</v>
       </c>
-      <c r="I5">
-        <v>0</v>
+      <c r="I5" t="s">
+        <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5">
-        <v>19235</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
+        <v>17367</v>
+      </c>
+      <c r="M5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" t="s">
+        <v>24</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1973,29 +1973,29 @@
       <c r="H6" t="s">
         <v>23</v>
       </c>
-      <c r="I6">
-        <v>0</v>
+      <c r="I6" t="s">
+        <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L6">
-        <v>21825</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
+        <v>25625</v>
+      </c>
+      <c r="M6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" t="s">
+        <v>24</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2006,13 +2006,13 @@
         <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
         <v>35</v>
@@ -2023,29 +2023,29 @@
       <c r="H7" t="s">
         <v>23</v>
       </c>
-      <c r="I7">
-        <v>0</v>
+      <c r="I7" t="s">
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7">
-        <v>17534</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
+        <v>22697</v>
+      </c>
+      <c r="M7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" t="s">
+        <v>24</v>
       </c>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2053,16 +2053,16 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
         <v>35</v>
@@ -2073,29 +2073,29 @@
       <c r="H8" t="s">
         <v>23</v>
       </c>
-      <c r="I8">
-        <v>0</v>
+      <c r="I8" t="s">
+        <v>24</v>
       </c>
       <c r="J8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L8">
-        <v>9314</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
+        <v>25817</v>
+      </c>
+      <c r="M8" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" t="s">
+        <v>24</v>
       </c>
       <c r="O8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2103,16 +2103,16 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
         <v>50</v>
       </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
         <v>35</v>
@@ -2123,29 +2123,29 @@
       <c r="H9" t="s">
         <v>23</v>
       </c>
-      <c r="I9">
-        <v>0</v>
+      <c r="I9" t="s">
+        <v>24</v>
       </c>
       <c r="J9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L9">
-        <v>17164</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
+        <v>26339</v>
+      </c>
+      <c r="M9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" t="s">
+        <v>24</v>
       </c>
       <c r="O9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2153,16 +2153,16 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
         <v>35</v>
@@ -2173,29 +2173,29 @@
       <c r="H10" t="s">
         <v>23</v>
       </c>
-      <c r="I10">
-        <v>0</v>
+      <c r="I10" t="s">
+        <v>24</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L10">
-        <v>21884</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
+        <v>22883</v>
+      </c>
+      <c r="M10" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" t="s">
+        <v>24</v>
       </c>
       <c r="O10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2203,16 +2203,16 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
         <v>35</v>
@@ -2223,29 +2223,29 @@
       <c r="H11" t="s">
         <v>23</v>
       </c>
-      <c r="I11">
-        <v>0</v>
+      <c r="I11" t="s">
+        <v>24</v>
       </c>
       <c r="J11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L11">
-        <v>13573</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
+        <v>18552</v>
+      </c>
+      <c r="M11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" t="s">
+        <v>24</v>
       </c>
       <c r="O11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2253,16 +2253,16 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s">
         <v>35</v>
@@ -2273,29 +2273,29 @@
       <c r="H12" t="s">
         <v>23</v>
       </c>
-      <c r="I12">
-        <v>0</v>
+      <c r="I12" t="s">
+        <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L12">
-        <v>17982</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
+        <v>19701</v>
+      </c>
+      <c r="M12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" t="s">
+        <v>24</v>
       </c>
       <c r="O12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2303,49 +2303,49 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13">
+        <v>17844</v>
+      </c>
+      <c r="M13" t="s">
+        <v>24</v>
+      </c>
+      <c r="N13" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" t="s">
         <v>64</v>
       </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13">
-        <v>23906</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>63</v>
-      </c>
       <c r="P13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2353,16 +2353,16 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
         <v>66</v>
       </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F14" t="s">
         <v>35</v>
@@ -2373,29 +2373,29 @@
       <c r="H14" t="s">
         <v>23</v>
       </c>
-      <c r="I14">
-        <v>0</v>
+      <c r="I14" t="s">
+        <v>24</v>
       </c>
       <c r="J14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L14">
-        <v>13149</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
+        <v>20782</v>
+      </c>
+      <c r="M14" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" t="s">
+        <v>24</v>
       </c>
       <c r="O14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2403,13 +2403,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
         <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
         <v>44</v>
@@ -2423,29 +2423,29 @@
       <c r="H15" t="s">
         <v>23</v>
       </c>
-      <c r="I15">
-        <v>0</v>
+      <c r="I15" t="s">
+        <v>24</v>
       </c>
       <c r="J15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L15">
-        <v>21682</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
+        <v>18462</v>
+      </c>
+      <c r="M15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" t="s">
+        <v>24</v>
       </c>
       <c r="O15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2453,16 +2453,16 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
         <v>35</v>
@@ -2473,29 +2473,29 @@
       <c r="H16" t="s">
         <v>23</v>
       </c>
-      <c r="I16">
-        <v>0</v>
+      <c r="I16" t="s">
+        <v>24</v>
       </c>
       <c r="J16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L16">
-        <v>16088</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
+        <v>15219</v>
+      </c>
+      <c r="M16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" t="s">
+        <v>24</v>
       </c>
       <c r="O16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2503,16 +2503,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s">
         <v>35</v>
@@ -2523,29 +2523,29 @@
       <c r="H17" t="s">
         <v>23</v>
       </c>
-      <c r="I17">
-        <v>0</v>
+      <c r="I17" t="s">
+        <v>24</v>
       </c>
       <c r="J17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L17">
-        <v>19023</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
+        <v>12302</v>
+      </c>
+      <c r="M17" t="s">
+        <v>24</v>
+      </c>
+      <c r="N17" t="s">
+        <v>24</v>
       </c>
       <c r="O17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P17" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2553,16 +2553,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F18" t="s">
         <v>35</v>
@@ -2573,29 +2573,29 @@
       <c r="H18" t="s">
         <v>23</v>
       </c>
-      <c r="I18">
-        <v>0</v>
+      <c r="I18" t="s">
+        <v>24</v>
       </c>
       <c r="J18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L18">
-        <v>19395</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
+        <v>14203</v>
+      </c>
+      <c r="M18" t="s">
+        <v>24</v>
+      </c>
+      <c r="N18" t="s">
+        <v>24</v>
       </c>
       <c r="O18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P18" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2603,16 +2603,16 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F19" t="s">
         <v>35</v>
@@ -2623,29 +2623,29 @@
       <c r="H19" t="s">
         <v>23</v>
       </c>
-      <c r="I19">
-        <v>0</v>
+      <c r="I19" t="s">
+        <v>24</v>
       </c>
       <c r="J19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L19">
-        <v>13623</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
+        <v>19571</v>
+      </c>
+      <c r="M19" t="s">
+        <v>24</v>
+      </c>
+      <c r="N19" t="s">
+        <v>24</v>
       </c>
       <c r="O19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2662,7 +2662,7 @@
         <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s">
         <v>35</v>
@@ -2673,29 +2673,29 @@
       <c r="H20" t="s">
         <v>23</v>
       </c>
-      <c r="I20">
-        <v>0</v>
+      <c r="I20" t="s">
+        <v>24</v>
       </c>
       <c r="J20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L20">
-        <v>11768</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
+        <v>19983</v>
+      </c>
+      <c r="M20" t="s">
+        <v>24</v>
+      </c>
+      <c r="N20" t="s">
+        <v>24</v>
       </c>
       <c r="O20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2706,13 +2706,13 @@
         <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
         <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F21" t="s">
         <v>35</v>
@@ -2723,29 +2723,29 @@
       <c r="H21" t="s">
         <v>23</v>
       </c>
-      <c r="I21">
-        <v>0</v>
+      <c r="I21" t="s">
+        <v>24</v>
       </c>
       <c r="J21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L21">
-        <v>19167</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
+        <v>22269</v>
+      </c>
+      <c r="M21" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" t="s">
+        <v>24</v>
       </c>
       <c r="O21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P21" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2756,13 +2756,13 @@
         <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
         <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F22" t="s">
         <v>35</v>
@@ -2773,29 +2773,29 @@
       <c r="H22" t="s">
         <v>23</v>
       </c>
-      <c r="I22">
-        <v>0</v>
+      <c r="I22" t="s">
+        <v>24</v>
       </c>
       <c r="J22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L22">
-        <v>14799</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
+        <v>16637</v>
+      </c>
+      <c r="M22" t="s">
+        <v>24</v>
+      </c>
+      <c r="N22" t="s">
+        <v>24</v>
       </c>
       <c r="O22" t="s">
         <v>87</v>
       </c>
       <c r="P22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2806,13 +2806,13 @@
         <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
         <v>89</v>
       </c>
       <c r="E23" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s">
         <v>35</v>
@@ -2823,29 +2823,29 @@
       <c r="H23" t="s">
         <v>23</v>
       </c>
-      <c r="I23">
-        <v>0</v>
+      <c r="I23" t="s">
+        <v>24</v>
       </c>
       <c r="J23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L23">
-        <v>18453</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
+        <v>24453</v>
+      </c>
+      <c r="M23" t="s">
+        <v>24</v>
+      </c>
+      <c r="N23" t="s">
+        <v>24</v>
       </c>
       <c r="O23" t="s">
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2856,7 +2856,7 @@
         <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
         <v>91</v>
@@ -2873,29 +2873,29 @@
       <c r="H24" t="s">
         <v>23</v>
       </c>
-      <c r="I24">
-        <v>0</v>
+      <c r="I24" t="s">
+        <v>24</v>
       </c>
       <c r="J24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L24">
-        <v>20191</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
+        <v>13715</v>
+      </c>
+      <c r="M24" t="s">
+        <v>24</v>
+      </c>
+      <c r="N24" t="s">
+        <v>24</v>
       </c>
       <c r="O24" t="s">
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2906,13 +2906,13 @@
         <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
         <v>93</v>
       </c>
       <c r="E25" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
         <v>35</v>
@@ -2923,29 +2923,29 @@
       <c r="H25" t="s">
         <v>23</v>
       </c>
-      <c r="I25">
-        <v>0</v>
+      <c r="I25" t="s">
+        <v>24</v>
       </c>
       <c r="J25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L25">
-        <v>17264</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
+        <v>9864</v>
+      </c>
+      <c r="M25" t="s">
+        <v>24</v>
+      </c>
+      <c r="N25" t="s">
+        <v>24</v>
       </c>
       <c r="O25" t="s">
         <v>87</v>
       </c>
       <c r="P25" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2956,13 +2956,13 @@
         <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D26" t="s">
         <v>95</v>
       </c>
       <c r="E26" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F26" t="s">
         <v>35</v>
@@ -2973,29 +2973,29 @@
       <c r="H26" t="s">
         <v>23</v>
       </c>
-      <c r="I26">
-        <v>0</v>
+      <c r="I26" t="s">
+        <v>24</v>
       </c>
       <c r="J26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L26">
-        <v>22278</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
+        <v>14118</v>
+      </c>
+      <c r="M26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N26" t="s">
+        <v>24</v>
       </c>
       <c r="O26" t="s">
         <v>87</v>
       </c>
       <c r="P26" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3023,29 +3023,29 @@
       <c r="H27" t="s">
         <v>23</v>
       </c>
-      <c r="I27">
-        <v>0</v>
+      <c r="I27" t="s">
+        <v>24</v>
       </c>
       <c r="J27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L27">
-        <v>25732</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
+        <v>22440</v>
+      </c>
+      <c r="M27" t="s">
+        <v>24</v>
+      </c>
+      <c r="N27" t="s">
+        <v>24</v>
       </c>
       <c r="O27" t="s">
         <v>87</v>
       </c>
       <c r="P27" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3056,13 +3056,13 @@
         <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D28" t="s">
         <v>99</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F28" t="s">
         <v>35</v>
@@ -3073,29 +3073,29 @@
       <c r="H28" t="s">
         <v>23</v>
       </c>
-      <c r="I28">
-        <v>0</v>
+      <c r="I28" t="s">
+        <v>24</v>
       </c>
       <c r="J28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L28">
-        <v>25215</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
+        <v>17712</v>
+      </c>
+      <c r="M28" t="s">
+        <v>24</v>
+      </c>
+      <c r="N28" t="s">
+        <v>24</v>
       </c>
       <c r="O28" t="s">
         <v>87</v>
       </c>
       <c r="P28" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3106,13 +3106,13 @@
         <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D29" t="s">
         <v>101</v>
       </c>
       <c r="E29" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F29" t="s">
         <v>35</v>
@@ -3123,29 +3123,29 @@
       <c r="H29" t="s">
         <v>23</v>
       </c>
-      <c r="I29">
-        <v>0</v>
+      <c r="I29" t="s">
+        <v>24</v>
       </c>
       <c r="J29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L29">
-        <v>22104</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
+        <v>18078</v>
+      </c>
+      <c r="M29" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" t="s">
+        <v>24</v>
       </c>
       <c r="O29" t="s">
         <v>87</v>
       </c>
       <c r="P29" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3156,13 +3156,13 @@
         <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
         <v>103</v>
       </c>
       <c r="E30" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F30" t="s">
         <v>35</v>
@@ -3173,29 +3173,29 @@
       <c r="H30" t="s">
         <v>23</v>
       </c>
-      <c r="I30">
-        <v>0</v>
+      <c r="I30" t="s">
+        <v>24</v>
       </c>
       <c r="J30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L30">
-        <v>25051</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
+        <v>22438</v>
+      </c>
+      <c r="M30" t="s">
+        <v>24</v>
+      </c>
+      <c r="N30" t="s">
+        <v>24</v>
       </c>
       <c r="O30" t="s">
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3206,13 +3206,13 @@
         <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D31" t="s">
         <v>105</v>
       </c>
       <c r="E31" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F31" t="s">
         <v>35</v>
@@ -3223,29 +3223,29 @@
       <c r="H31" t="s">
         <v>23</v>
       </c>
-      <c r="I31">
-        <v>0</v>
+      <c r="I31" t="s">
+        <v>24</v>
       </c>
       <c r="J31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L31">
-        <v>16775</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
+        <v>19777</v>
+      </c>
+      <c r="M31" t="s">
+        <v>24</v>
+      </c>
+      <c r="N31" t="s">
+        <v>24</v>
       </c>
       <c r="O31" t="s">
         <v>87</v>
       </c>
       <c r="P31" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3256,14 +3256,14 @@
         <v>106</v>
       </c>
       <c r="C32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" t="s">
         <v>107</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>108</v>
       </c>
-      <c r="E32" t="s">
-        <v>49</v>
-      </c>
       <c r="F32" t="s">
         <v>35</v>
       </c>
@@ -3273,29 +3273,29 @@
       <c r="H32" t="s">
         <v>23</v>
       </c>
-      <c r="I32">
-        <v>0</v>
+      <c r="I32" t="s">
+        <v>24</v>
       </c>
       <c r="J32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L32">
-        <v>16108</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
+        <v>13002</v>
+      </c>
+      <c r="M32" t="s">
+        <v>24</v>
+      </c>
+      <c r="N32" t="s">
+        <v>24</v>
       </c>
       <c r="O32" t="s">
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3306,13 +3306,13 @@
         <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s">
         <v>111</v>
       </c>
       <c r="E33" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F33" t="s">
         <v>35</v>
@@ -3323,29 +3323,29 @@
       <c r="H33" t="s">
         <v>23</v>
       </c>
-      <c r="I33">
-        <v>0</v>
+      <c r="I33" t="s">
+        <v>24</v>
       </c>
       <c r="J33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L33">
-        <v>8797</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
+        <v>16974</v>
+      </c>
+      <c r="M33" t="s">
+        <v>24</v>
+      </c>
+      <c r="N33" t="s">
+        <v>24</v>
       </c>
       <c r="O33" t="s">
         <v>109</v>
       </c>
       <c r="P33" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3356,13 +3356,13 @@
         <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
         <v>113</v>
       </c>
       <c r="E34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
         <v>35</v>
@@ -3373,29 +3373,29 @@
       <c r="H34" t="s">
         <v>23</v>
       </c>
-      <c r="I34">
-        <v>0</v>
+      <c r="I34" t="s">
+        <v>24</v>
       </c>
       <c r="J34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L34">
-        <v>17295</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
+        <v>11207</v>
+      </c>
+      <c r="M34" t="s">
+        <v>24</v>
+      </c>
+      <c r="N34" t="s">
+        <v>24</v>
       </c>
       <c r="O34" t="s">
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3406,13 +3406,13 @@
         <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D35" t="s">
         <v>115</v>
       </c>
       <c r="E35" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F35" t="s">
         <v>35</v>
@@ -3423,29 +3423,29 @@
       <c r="H35" t="s">
         <v>23</v>
       </c>
-      <c r="I35">
-        <v>0</v>
+      <c r="I35" t="s">
+        <v>24</v>
       </c>
       <c r="J35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L35">
-        <v>1146</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
+        <v>1463</v>
+      </c>
+      <c r="M35" t="s">
+        <v>24</v>
+      </c>
+      <c r="N35" t="s">
+        <v>24</v>
       </c>
       <c r="O35" t="s">
         <v>109</v>
       </c>
       <c r="P35" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3456,13 +3456,13 @@
         <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D36" t="s">
         <v>117</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F36" t="s">
         <v>35</v>
@@ -3473,29 +3473,29 @@
       <c r="H36" t="s">
         <v>23</v>
       </c>
-      <c r="I36">
-        <v>0</v>
+      <c r="I36" t="s">
+        <v>24</v>
       </c>
       <c r="J36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L36">
-        <v>19280</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
+        <v>6379</v>
+      </c>
+      <c r="M36" t="s">
+        <v>24</v>
+      </c>
+      <c r="N36" t="s">
+        <v>24</v>
       </c>
       <c r="O36" t="s">
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3506,13 +3506,13 @@
         <v>118</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="D37" t="s">
         <v>119</v>
       </c>
       <c r="E37" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F37" t="s">
         <v>35</v>
@@ -3523,29 +3523,29 @@
       <c r="H37" t="s">
         <v>23</v>
       </c>
-      <c r="I37">
-        <v>0</v>
+      <c r="I37" t="s">
+        <v>24</v>
       </c>
       <c r="J37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L37">
-        <v>16493</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
+        <v>5419</v>
+      </c>
+      <c r="M37" t="s">
+        <v>24</v>
+      </c>
+      <c r="N37" t="s">
+        <v>24</v>
       </c>
       <c r="O37" t="s">
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3556,13 +3556,13 @@
         <v>120</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D38" t="s">
         <v>121</v>
       </c>
       <c r="E38" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="F38" t="s">
         <v>35</v>
@@ -3573,29 +3573,29 @@
       <c r="H38" t="s">
         <v>23</v>
       </c>
-      <c r="I38">
-        <v>0</v>
+      <c r="I38" t="s">
+        <v>24</v>
       </c>
       <c r="J38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L38">
-        <v>17459</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
+        <v>19589</v>
+      </c>
+      <c r="M38" t="s">
+        <v>24</v>
+      </c>
+      <c r="N38" t="s">
+        <v>24</v>
       </c>
       <c r="O38" t="s">
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3603,49 +3603,49 @@
         <v>16</v>
       </c>
       <c r="B39" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D39" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E39" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F39" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="G39" t="s">
         <v>36</v>
       </c>
       <c r="H39" t="s">
-        <v>23</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
+        <v>126</v>
+      </c>
+      <c r="I39" t="s">
+        <v>24</v>
       </c>
       <c r="J39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L39">
-        <v>4835</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
+        <v>22000</v>
+      </c>
+      <c r="M39" t="s">
+        <v>24</v>
+      </c>
+      <c r="N39" t="s">
+        <v>24</v>
       </c>
       <c r="O39" t="s">
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3653,16 +3653,16 @@
         <v>16</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C40" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D40" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E40" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F40" t="s">
         <v>35</v>
@@ -3673,29 +3673,29 @@
       <c r="H40" t="s">
         <v>23</v>
       </c>
-      <c r="I40">
-        <v>0</v>
+      <c r="I40" t="s">
+        <v>24</v>
       </c>
       <c r="J40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L40">
-        <v>18009</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
+        <v>2489</v>
+      </c>
+      <c r="M40" t="s">
+        <v>24</v>
+      </c>
+      <c r="N40" t="s">
+        <v>24</v>
       </c>
       <c r="O40" t="s">
         <v>109</v>
       </c>
       <c r="P40" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3703,16 +3703,16 @@
         <v>16</v>
       </c>
       <c r="B41" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E41" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F41" t="s">
         <v>35</v>
@@ -3723,29 +3723,29 @@
       <c r="H41" t="s">
         <v>23</v>
       </c>
-      <c r="I41">
-        <v>0</v>
+      <c r="I41" t="s">
+        <v>24</v>
       </c>
       <c r="J41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L41">
-        <v>12331</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
+        <v>1727</v>
+      </c>
+      <c r="M41" t="s">
+        <v>24</v>
+      </c>
+      <c r="N41" t="s">
+        <v>24</v>
       </c>
       <c r="O41" t="s">
         <v>109</v>
       </c>
       <c r="P41" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3753,13 +3753,13 @@
         <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s">
         <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
         <v>44</v>
@@ -3773,29 +3773,29 @@
       <c r="H42" t="s">
         <v>23</v>
       </c>
-      <c r="I42">
-        <v>0</v>
+      <c r="I42" t="s">
+        <v>24</v>
       </c>
       <c r="J42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L42">
-        <v>19846</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
+        <v>17467</v>
+      </c>
+      <c r="M42" t="s">
+        <v>24</v>
+      </c>
+      <c r="N42" t="s">
+        <v>24</v>
       </c>
       <c r="O42" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P42" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3803,49 +3803,49 @@
         <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D43" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E43" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="G43" t="s">
         <v>36</v>
       </c>
       <c r="H43" t="s">
-        <v>23</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
+        <v>126</v>
+      </c>
+      <c r="I43" t="s">
+        <v>24</v>
       </c>
       <c r="J43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L43">
-        <v>9498</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
+        <v>13087</v>
+      </c>
+      <c r="M43" t="s">
+        <v>24</v>
+      </c>
+      <c r="N43" t="s">
+        <v>24</v>
       </c>
       <c r="O43" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P43" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3853,49 +3853,49 @@
         <v>16</v>
       </c>
       <c r="B44" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F44" t="s">
+        <v>35</v>
+      </c>
+      <c r="G44" t="s">
+        <v>36</v>
+      </c>
+      <c r="H44" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" t="s">
+        <v>24</v>
+      </c>
+      <c r="J44" t="s">
+        <v>25</v>
+      </c>
+      <c r="K44" t="s">
+        <v>26</v>
+      </c>
+      <c r="L44">
+        <v>17901</v>
+      </c>
+      <c r="M44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N44" t="s">
+        <v>24</v>
+      </c>
+      <c r="O44" t="s">
         <v>133</v>
       </c>
-      <c r="C44" t="s">
-        <v>78</v>
-      </c>
-      <c r="D44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E44" t="s">
-        <v>80</v>
-      </c>
-      <c r="F44" t="s">
-        <v>35</v>
-      </c>
-      <c r="G44" t="s">
-        <v>36</v>
-      </c>
-      <c r="H44" t="s">
-        <v>23</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44" t="s">
-        <v>24</v>
-      </c>
-      <c r="K44" t="s">
-        <v>25</v>
-      </c>
-      <c r="L44">
-        <v>14127</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44" t="s">
-        <v>130</v>
-      </c>
       <c r="P44" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3903,16 +3903,16 @@
         <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D45" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E45" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F45" t="s">
         <v>35</v>
@@ -3923,29 +3923,29 @@
       <c r="H45" t="s">
         <v>23</v>
       </c>
-      <c r="I45">
-        <v>0</v>
+      <c r="I45" t="s">
+        <v>24</v>
       </c>
       <c r="J45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L45">
-        <v>474</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
+        <v>2230</v>
+      </c>
+      <c r="M45" t="s">
+        <v>24</v>
+      </c>
+      <c r="N45" t="s">
+        <v>24</v>
       </c>
       <c r="O45" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P45" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3953,16 +3953,16 @@
         <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C46" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D46" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E46" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="F46" t="s">
         <v>35</v>
@@ -3971,31 +3971,31 @@
         <v>36</v>
       </c>
       <c r="H46" t="s">
-        <v>140</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I46" t="s">
+        <v>24</v>
       </c>
       <c r="J46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L46">
-        <v>3769</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="M46" t="s">
+        <v>24</v>
+      </c>
+      <c r="N46" t="s">
+        <v>24</v>
       </c>
       <c r="O46" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P46" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4003,16 +4003,16 @@
         <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E47" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F47" t="s">
         <v>35</v>
@@ -4023,29 +4023,29 @@
       <c r="H47" t="s">
         <v>23</v>
       </c>
-      <c r="I47">
-        <v>0</v>
+      <c r="I47" t="s">
+        <v>24</v>
       </c>
       <c r="J47" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K47" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L47">
-        <v>10159</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
+        <v>14709</v>
+      </c>
+      <c r="M47" t="s">
+        <v>24</v>
+      </c>
+      <c r="N47" t="s">
+        <v>24</v>
       </c>
       <c r="O47" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P47" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4053,16 +4053,16 @@
         <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F48" t="s">
         <v>35</v>
@@ -4073,29 +4073,29 @@
       <c r="H48" t="s">
         <v>23</v>
       </c>
-      <c r="I48">
-        <v>0</v>
+      <c r="I48" t="s">
+        <v>24</v>
       </c>
       <c r="J48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L48">
-        <v>10004</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
+        <v>476</v>
+      </c>
+      <c r="M48" t="s">
+        <v>24</v>
+      </c>
+      <c r="N48" t="s">
+        <v>24</v>
       </c>
       <c r="O48" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P48" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4103,16 +4103,16 @@
         <v>16</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E49" t="s">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="F49" t="s">
         <v>35</v>
@@ -4121,31 +4121,31 @@
         <v>36</v>
       </c>
       <c r="H49" t="s">
-        <v>23</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
+        <v>126</v>
+      </c>
+      <c r="I49" t="s">
+        <v>24</v>
       </c>
       <c r="J49" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L49">
-        <v>11</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
+        <v>4359</v>
+      </c>
+      <c r="M49" t="s">
+        <v>24</v>
+      </c>
+      <c r="N49" t="s">
+        <v>24</v>
       </c>
       <c r="O49" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P49" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4153,16 +4153,16 @@
         <v>16</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C50" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E50" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F50" t="s">
         <v>35</v>
@@ -4173,29 +4173,29 @@
       <c r="H50" t="s">
         <v>23</v>
       </c>
-      <c r="I50">
-        <v>0</v>
+      <c r="I50" t="s">
+        <v>24</v>
       </c>
       <c r="J50" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L50">
-        <v>1698</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
+        <v>10167</v>
+      </c>
+      <c r="M50" t="s">
+        <v>24</v>
+      </c>
+      <c r="N50" t="s">
+        <v>24</v>
       </c>
       <c r="O50" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P50" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4203,16 +4203,16 @@
         <v>16</v>
       </c>
       <c r="B51" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C51" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E51" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F51" t="s">
         <v>35</v>
@@ -4223,29 +4223,29 @@
       <c r="H51" t="s">
         <v>23</v>
       </c>
-      <c r="I51">
-        <v>0</v>
+      <c r="I51" t="s">
+        <v>24</v>
       </c>
       <c r="J51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L51">
-        <v>17892</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
+        <v>10012</v>
+      </c>
+      <c r="M51" t="s">
+        <v>24</v>
+      </c>
+      <c r="N51" t="s">
+        <v>24</v>
       </c>
       <c r="O51" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P51" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4253,49 +4253,49 @@
         <v>16</v>
       </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D52" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E52" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="F52" t="s">
-        <v>153</v>
+        <v>35</v>
       </c>
       <c r="G52" t="s">
         <v>36</v>
       </c>
       <c r="H52" t="s">
-        <v>140</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I52" t="s">
+        <v>24</v>
       </c>
       <c r="J52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L52">
-        <v>12497</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
+        <v>9502</v>
+      </c>
+      <c r="M52" t="s">
+        <v>24</v>
+      </c>
+      <c r="N52" t="s">
+        <v>24</v>
       </c>
       <c r="O52" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P52" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4303,49 +4303,49 @@
         <v>16</v>
       </c>
       <c r="B53" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D53" t="s">
+        <v>157</v>
+      </c>
+      <c r="E53" t="s">
+        <v>52</v>
+      </c>
+      <c r="F53" t="s">
+        <v>35</v>
+      </c>
+      <c r="G53" t="s">
+        <v>36</v>
+      </c>
+      <c r="H53" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" t="s">
+        <v>24</v>
+      </c>
+      <c r="J53" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53">
+        <v>20426</v>
+      </c>
+      <c r="M53" t="s">
+        <v>24</v>
+      </c>
+      <c r="N53" t="s">
+        <v>24</v>
+      </c>
+      <c r="O53" t="s">
         <v>155</v>
       </c>
-      <c r="C53" t="s">
-        <v>38</v>
-      </c>
-      <c r="D53" t="s">
-        <v>156</v>
-      </c>
-      <c r="E53" t="s">
-        <v>40</v>
-      </c>
-      <c r="F53" t="s">
-        <v>35</v>
-      </c>
-      <c r="G53" t="s">
-        <v>36</v>
-      </c>
-      <c r="H53" t="s">
-        <v>23</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53" t="s">
-        <v>24</v>
-      </c>
-      <c r="K53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L53">
-        <v>1710</v>
-      </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53" t="s">
-        <v>154</v>
-      </c>
       <c r="P53" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4353,16 +4353,16 @@
         <v>16</v>
       </c>
       <c r="B54" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C54" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D54" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E54" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F54" t="s">
         <v>35</v>
@@ -4373,29 +4373,29 @@
       <c r="H54" t="s">
         <v>23</v>
       </c>
-      <c r="I54">
-        <v>0</v>
+      <c r="I54" t="s">
+        <v>24</v>
       </c>
       <c r="J54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L54">
-        <v>2485</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
+        <v>12867</v>
+      </c>
+      <c r="M54" t="s">
+        <v>24</v>
+      </c>
+      <c r="N54" t="s">
+        <v>24</v>
       </c>
       <c r="O54" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P54" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4403,49 +4403,49 @@
         <v>16</v>
       </c>
       <c r="B55" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D55" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E55" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="F55" t="s">
-        <v>153</v>
+        <v>35</v>
       </c>
       <c r="G55" t="s">
         <v>36</v>
       </c>
       <c r="H55" t="s">
-        <v>140</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I55" t="s">
+        <v>24</v>
       </c>
       <c r="J55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L55">
-        <v>21403</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
+        <v>19857</v>
+      </c>
+      <c r="M55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N55" t="s">
+        <v>24</v>
       </c>
       <c r="O55" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P55" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4453,16 +4453,16 @@
         <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E56" t="s">
-        <v>163</v>
+        <v>34</v>
       </c>
       <c r="F56" t="s">
         <v>35</v>
@@ -4473,29 +4473,29 @@
       <c r="H56" t="s">
         <v>23</v>
       </c>
-      <c r="I56">
-        <v>0</v>
+      <c r="I56" t="s">
+        <v>24</v>
       </c>
       <c r="J56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L56">
-        <v>18999</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
+        <v>16498</v>
+      </c>
+      <c r="M56" t="s">
+        <v>24</v>
+      </c>
+      <c r="N56" t="s">
+        <v>24</v>
       </c>
       <c r="O56" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P56" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4506,13 +4506,13 @@
         <v>164</v>
       </c>
       <c r="C57" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="D57" t="s">
         <v>165</v>
       </c>
       <c r="E57" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F57" t="s">
         <v>35</v>
@@ -4523,29 +4523,29 @@
       <c r="H57" t="s">
         <v>23</v>
       </c>
-      <c r="I57">
-        <v>0</v>
+      <c r="I57" t="s">
+        <v>24</v>
       </c>
       <c r="J57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L57">
-        <v>11198</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
+        <v>1387</v>
+      </c>
+      <c r="M57" t="s">
+        <v>24</v>
+      </c>
+      <c r="N57" t="s">
+        <v>24</v>
       </c>
       <c r="O57" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P57" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4573,29 +4573,29 @@
       <c r="H58" t="s">
         <v>23</v>
       </c>
-      <c r="I58">
-        <v>0</v>
+      <c r="I58" t="s">
+        <v>24</v>
       </c>
       <c r="J58" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L58">
-        <v>5795</v>
-      </c>
-      <c r="M58">
-        <v>0</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
+        <v>17300</v>
+      </c>
+      <c r="M58" t="s">
+        <v>24</v>
+      </c>
+      <c r="N58" t="s">
+        <v>24</v>
       </c>
       <c r="O58" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P58" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4606,13 +4606,13 @@
         <v>168</v>
       </c>
       <c r="C59" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D59" t="s">
         <v>169</v>
       </c>
       <c r="E59" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F59" t="s">
         <v>35</v>
@@ -4623,29 +4623,29 @@
       <c r="H59" t="s">
         <v>23</v>
       </c>
-      <c r="I59">
-        <v>0</v>
+      <c r="I59" t="s">
+        <v>24</v>
       </c>
       <c r="J59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K59" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L59">
-        <v>16965</v>
-      </c>
-      <c r="M59">
-        <v>0</v>
-      </c>
-      <c r="N59">
-        <v>0</v>
+        <v>8800</v>
+      </c>
+      <c r="M59" t="s">
+        <v>24</v>
+      </c>
+      <c r="N59" t="s">
+        <v>24</v>
       </c>
       <c r="O59" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P59" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4662,7 +4662,7 @@
         <v>171</v>
       </c>
       <c r="E60" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F60" t="s">
         <v>35</v>
@@ -4673,29 +4673,29 @@
       <c r="H60" t="s">
         <v>23</v>
       </c>
-      <c r="I60">
-        <v>0</v>
+      <c r="I60" t="s">
+        <v>24</v>
       </c>
       <c r="J60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K60" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L60">
-        <v>1460</v>
-      </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
+        <v>18015</v>
+      </c>
+      <c r="M60" t="s">
+        <v>24</v>
+      </c>
+      <c r="N60" t="s">
+        <v>24</v>
       </c>
       <c r="O60" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P60" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4706,13 +4706,13 @@
         <v>172</v>
       </c>
       <c r="C61" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D61" t="s">
         <v>173</v>
       </c>
       <c r="E61" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="F61" t="s">
         <v>35</v>
@@ -4721,31 +4721,31 @@
         <v>36</v>
       </c>
       <c r="H61" t="s">
-        <v>140</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I61" t="s">
+        <v>24</v>
       </c>
       <c r="J61" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L61">
-        <v>3795</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
+        <v>8711</v>
+      </c>
+      <c r="M61" t="s">
+        <v>24</v>
+      </c>
+      <c r="N61" t="s">
+        <v>24</v>
       </c>
       <c r="O61" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P61" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4756,13 +4756,13 @@
         <v>174</v>
       </c>
       <c r="C62" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D62" t="s">
         <v>175</v>
       </c>
       <c r="E62" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F62" t="s">
         <v>35</v>
@@ -4773,29 +4773,29 @@
       <c r="H62" t="s">
         <v>23</v>
       </c>
-      <c r="I62">
-        <v>0</v>
+      <c r="I62" t="s">
+        <v>24</v>
       </c>
       <c r="J62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L62">
-        <v>4426</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
+        <v>17752</v>
+      </c>
+      <c r="M62" t="s">
+        <v>24</v>
+      </c>
+      <c r="N62" t="s">
+        <v>24</v>
       </c>
       <c r="O62" t="s">
         <v>176</v>
       </c>
       <c r="P62" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4806,13 +4806,13 @@
         <v>177</v>
       </c>
       <c r="C63" t="s">
-        <v>42</v>
+        <v>178</v>
       </c>
       <c r="D63" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E63" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F63" t="s">
         <v>35</v>
@@ -4823,29 +4823,29 @@
       <c r="H63" t="s">
         <v>23</v>
       </c>
-      <c r="I63">
-        <v>0</v>
+      <c r="I63" t="s">
+        <v>24</v>
       </c>
       <c r="J63" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L63">
-        <v>19835</v>
-      </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
+        <v>2143</v>
+      </c>
+      <c r="M63" t="s">
+        <v>24</v>
+      </c>
+      <c r="N63" t="s">
+        <v>24</v>
       </c>
       <c r="O63" t="s">
         <v>176</v>
       </c>
       <c r="P63" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4853,16 +4853,16 @@
         <v>16</v>
       </c>
       <c r="B64" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D64" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E64" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F64" t="s">
         <v>35</v>
@@ -4873,29 +4873,29 @@
       <c r="H64" t="s">
         <v>23</v>
       </c>
-      <c r="I64">
-        <v>0</v>
+      <c r="I64" t="s">
+        <v>24</v>
       </c>
       <c r="J64" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L64">
-        <v>4231</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-      <c r="N64">
-        <v>0</v>
+        <v>20384</v>
+      </c>
+      <c r="M64" t="s">
+        <v>24</v>
+      </c>
+      <c r="N64" t="s">
+        <v>24</v>
       </c>
       <c r="O64" t="s">
         <v>176</v>
       </c>
       <c r="P64" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4903,16 +4903,16 @@
         <v>16</v>
       </c>
       <c r="B65" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C65" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D65" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E65" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F65" t="s">
         <v>35</v>
@@ -4923,29 +4923,29 @@
       <c r="H65" t="s">
         <v>23</v>
       </c>
-      <c r="I65">
-        <v>0</v>
+      <c r="I65" t="s">
+        <v>24</v>
       </c>
       <c r="J65" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L65">
-        <v>475</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
+        <v>471</v>
+      </c>
+      <c r="M65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N65" t="s">
+        <v>24</v>
       </c>
       <c r="O65" t="s">
         <v>176</v>
       </c>
       <c r="P65" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4953,16 +4953,16 @@
         <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C66" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D66" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E66" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="F66" t="s">
         <v>35</v>
@@ -4973,29 +4973,29 @@
       <c r="H66" t="s">
         <v>23</v>
       </c>
-      <c r="I66">
-        <v>0</v>
+      <c r="I66" t="s">
+        <v>24</v>
       </c>
       <c r="J66" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K66" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L66">
-        <v>11625</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
+        <v>1860</v>
+      </c>
+      <c r="M66" t="s">
+        <v>24</v>
+      </c>
+      <c r="N66" t="s">
+        <v>24</v>
       </c>
       <c r="O66" t="s">
         <v>176</v>
       </c>
       <c r="P66" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5003,16 +5003,16 @@
         <v>16</v>
       </c>
       <c r="B67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C67" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="D67" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E67" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F67" t="s">
         <v>35</v>
@@ -5023,29 +5023,29 @@
       <c r="H67" t="s">
         <v>23</v>
       </c>
-      <c r="I67">
-        <v>0</v>
+      <c r="I67" t="s">
+        <v>24</v>
       </c>
       <c r="J67" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L67">
-        <v>17752</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
+        <v>1944</v>
+      </c>
+      <c r="M67" t="s">
+        <v>24</v>
+      </c>
+      <c r="N67" t="s">
+        <v>24</v>
       </c>
       <c r="O67" t="s">
         <v>176</v>
       </c>
       <c r="P67" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5053,16 +5053,16 @@
         <v>16</v>
       </c>
       <c r="B68" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C68" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D68" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E68" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F68" t="s">
         <v>35</v>
@@ -5073,29 +5073,29 @@
       <c r="H68" t="s">
         <v>23</v>
       </c>
-      <c r="I68">
-        <v>0</v>
+      <c r="I68" t="s">
+        <v>24</v>
       </c>
       <c r="J68" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L68">
-        <v>10397</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
+        <v>4910</v>
+      </c>
+      <c r="M68" t="s">
+        <v>24</v>
+      </c>
+      <c r="N68" t="s">
+        <v>24</v>
       </c>
       <c r="O68" t="s">
         <v>176</v>
       </c>
       <c r="P68" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5103,16 +5103,16 @@
         <v>16</v>
       </c>
       <c r="B69" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C69" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="D69" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E69" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F69" t="s">
         <v>35</v>
@@ -5123,29 +5123,29 @@
       <c r="H69" t="s">
         <v>23</v>
       </c>
-      <c r="I69">
-        <v>0</v>
+      <c r="I69" t="s">
+        <v>24</v>
       </c>
       <c r="J69" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L69">
-        <v>1914</v>
-      </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="M69" t="s">
+        <v>24</v>
+      </c>
+      <c r="N69" t="s">
+        <v>24</v>
       </c>
       <c r="O69" t="s">
         <v>176</v>
       </c>
       <c r="P69" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5153,16 +5153,16 @@
         <v>16</v>
       </c>
       <c r="B70" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C70" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D70" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F70" t="s">
         <v>35</v>
@@ -5173,29 +5173,29 @@
       <c r="H70" t="s">
         <v>23</v>
       </c>
-      <c r="I70">
-        <v>0</v>
+      <c r="I70" t="s">
+        <v>24</v>
       </c>
       <c r="J70" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L70">
-        <v>3342</v>
-      </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
+        <v>11309</v>
+      </c>
+      <c r="M70" t="s">
+        <v>24</v>
+      </c>
+      <c r="N70" t="s">
+        <v>24</v>
       </c>
       <c r="O70" t="s">
         <v>176</v>
       </c>
       <c r="P70" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5203,13 +5203,13 @@
         <v>16</v>
       </c>
       <c r="B71" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C71" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D71" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E71" t="s">
         <v>40</v>
@@ -5223,29 +5223,29 @@
       <c r="H71" t="s">
         <v>23</v>
       </c>
-      <c r="I71">
-        <v>0</v>
+      <c r="I71" t="s">
+        <v>24</v>
       </c>
       <c r="J71" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L71">
-        <v>1494</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
+        <v>8729</v>
+      </c>
+      <c r="M71" t="s">
+        <v>24</v>
+      </c>
+      <c r="N71" t="s">
+        <v>24</v>
       </c>
       <c r="O71" t="s">
         <v>176</v>
       </c>
       <c r="P71" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5253,16 +5253,16 @@
         <v>16</v>
       </c>
       <c r="B72" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C72" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D72" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E72" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F72" t="s">
         <v>35</v>
@@ -5273,29 +5273,29 @@
       <c r="H72" t="s">
         <v>23</v>
       </c>
-      <c r="I72">
-        <v>0</v>
+      <c r="I72" t="s">
+        <v>24</v>
       </c>
       <c r="J72" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L72">
-        <v>2583</v>
-      </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
-      <c r="N72">
-        <v>0</v>
+        <v>3132</v>
+      </c>
+      <c r="M72" t="s">
+        <v>24</v>
+      </c>
+      <c r="N72" t="s">
+        <v>24</v>
       </c>
       <c r="O72" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P72" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5303,49 +5303,49 @@
         <v>16</v>
       </c>
       <c r="B73" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C73" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="D73" t="s">
+        <v>201</v>
+      </c>
+      <c r="E73" t="s">
+        <v>68</v>
+      </c>
+      <c r="F73" t="s">
+        <v>35</v>
+      </c>
+      <c r="G73" t="s">
+        <v>36</v>
+      </c>
+      <c r="H73" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" t="s">
+        <v>24</v>
+      </c>
+      <c r="J73" t="s">
+        <v>25</v>
+      </c>
+      <c r="K73" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73">
+        <v>470</v>
+      </c>
+      <c r="M73" t="s">
+        <v>24</v>
+      </c>
+      <c r="N73" t="s">
+        <v>24</v>
+      </c>
+      <c r="O73" t="s">
         <v>199</v>
       </c>
-      <c r="E73" t="s">
-        <v>58</v>
-      </c>
-      <c r="F73" t="s">
-        <v>35</v>
-      </c>
-      <c r="G73" t="s">
-        <v>36</v>
-      </c>
-      <c r="H73" t="s">
-        <v>23</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73" t="s">
-        <v>24</v>
-      </c>
-      <c r="K73" t="s">
-        <v>25</v>
-      </c>
-      <c r="L73">
-        <v>8723</v>
-      </c>
-      <c r="M73">
-        <v>0</v>
-      </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73" t="s">
-        <v>197</v>
-      </c>
       <c r="P73" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5353,16 +5353,16 @@
         <v>16</v>
       </c>
       <c r="B74" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C74" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D74" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E74" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F74" t="s">
         <v>35</v>
@@ -5373,29 +5373,29 @@
       <c r="H74" t="s">
         <v>23</v>
       </c>
-      <c r="I74">
-        <v>0</v>
+      <c r="I74" t="s">
+        <v>24</v>
       </c>
       <c r="J74" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K74" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L74">
-        <v>11301</v>
-      </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
+        <v>1499</v>
+      </c>
+      <c r="M74" t="s">
+        <v>24</v>
+      </c>
+      <c r="N74" t="s">
+        <v>24</v>
       </c>
       <c r="O74" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P74" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5403,16 +5403,16 @@
         <v>16</v>
       </c>
       <c r="B75" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C75" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D75" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E75" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F75" t="s">
         <v>35</v>
@@ -5423,29 +5423,29 @@
       <c r="H75" t="s">
         <v>23</v>
       </c>
-      <c r="I75">
-        <v>0</v>
+      <c r="I75" t="s">
+        <v>24</v>
       </c>
       <c r="J75" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K75" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L75">
-        <v>26</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75">
-        <v>0</v>
+        <v>3925</v>
+      </c>
+      <c r="M75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N75" t="s">
+        <v>24</v>
       </c>
       <c r="O75" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P75" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5453,16 +5453,16 @@
         <v>16</v>
       </c>
       <c r="B76" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C76" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E76" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="F76" t="s">
         <v>35</v>
@@ -5473,29 +5473,29 @@
       <c r="H76" t="s">
         <v>23</v>
       </c>
-      <c r="I76">
-        <v>0</v>
+      <c r="I76" t="s">
+        <v>24</v>
       </c>
       <c r="J76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L76">
-        <v>4327</v>
-      </c>
-      <c r="M76">
-        <v>0</v>
-      </c>
-      <c r="N76">
-        <v>0</v>
+        <v>1920</v>
+      </c>
+      <c r="M76" t="s">
+        <v>24</v>
+      </c>
+      <c r="N76" t="s">
+        <v>24</v>
       </c>
       <c r="O76" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P76" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5503,16 +5503,16 @@
         <v>16</v>
       </c>
       <c r="B77" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C77" t="s">
-        <v>207</v>
+        <v>66</v>
       </c>
       <c r="D77" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E77" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F77" t="s">
         <v>35</v>
@@ -5523,29 +5523,29 @@
       <c r="H77" t="s">
         <v>23</v>
       </c>
-      <c r="I77">
-        <v>0</v>
+      <c r="I77" t="s">
+        <v>24</v>
       </c>
       <c r="J77" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L77">
-        <v>1936</v>
-      </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
-      <c r="N77">
-        <v>0</v>
+        <v>10402</v>
+      </c>
+      <c r="M77" t="s">
+        <v>24</v>
+      </c>
+      <c r="N77" t="s">
+        <v>24</v>
       </c>
       <c r="O77" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P77" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5553,16 +5553,16 @@
         <v>16</v>
       </c>
       <c r="B78" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C78" t="s">
         <v>42</v>
       </c>
       <c r="D78" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E78" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F78" t="s">
         <v>35</v>
@@ -5573,29 +5573,29 @@
       <c r="H78" t="s">
         <v>23</v>
       </c>
-      <c r="I78">
-        <v>0</v>
+      <c r="I78" t="s">
+        <v>24</v>
       </c>
       <c r="J78" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L78">
-        <v>1860</v>
-      </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
-      <c r="N78">
-        <v>0</v>
+        <v>17756</v>
+      </c>
+      <c r="M78" t="s">
+        <v>24</v>
+      </c>
+      <c r="N78" t="s">
+        <v>24</v>
       </c>
       <c r="O78" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P78" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5603,16 +5603,16 @@
         <v>16</v>
       </c>
       <c r="B79" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C79" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D79" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E79" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F79" t="s">
         <v>35</v>
@@ -5623,29 +5623,29 @@
       <c r="H79" t="s">
         <v>23</v>
       </c>
-      <c r="I79">
-        <v>0</v>
+      <c r="I79" t="s">
+        <v>24</v>
       </c>
       <c r="J79" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L79">
-        <v>471</v>
-      </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
+        <v>11631</v>
+      </c>
+      <c r="M79" t="s">
+        <v>24</v>
+      </c>
+      <c r="N79" t="s">
+        <v>24</v>
       </c>
       <c r="O79" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P79" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5653,16 +5653,16 @@
         <v>16</v>
       </c>
       <c r="B80" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C80" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D80" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E80" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F80" t="s">
         <v>35</v>
@@ -5673,29 +5673,29 @@
       <c r="H80" t="s">
         <v>23</v>
       </c>
-      <c r="I80">
-        <v>0</v>
+      <c r="I80" t="s">
+        <v>24</v>
       </c>
       <c r="J80" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K80" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L80">
-        <v>19799</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
+        <v>475</v>
+      </c>
+      <c r="M80" t="s">
+        <v>24</v>
+      </c>
+      <c r="N80" t="s">
+        <v>24</v>
       </c>
       <c r="O80" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P80" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5703,16 +5703,16 @@
         <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C81" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D81" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E81" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F81" t="s">
         <v>35</v>
@@ -5723,29 +5723,29 @@
       <c r="H81" t="s">
         <v>23</v>
       </c>
-      <c r="I81">
-        <v>0</v>
+      <c r="I81" t="s">
+        <v>24</v>
       </c>
       <c r="J81" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L81">
-        <v>8131</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81">
-        <v>0</v>
+        <v>4812</v>
+      </c>
+      <c r="M81" t="s">
+        <v>24</v>
+      </c>
+      <c r="N81" t="s">
+        <v>24</v>
       </c>
       <c r="O81" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P81" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5753,16 +5753,16 @@
         <v>16</v>
       </c>
       <c r="B82" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C82" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D82" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E82" t="s">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="F82" t="s">
         <v>35</v>
@@ -5771,31 +5771,31 @@
         <v>36</v>
       </c>
       <c r="H82" t="s">
-        <v>23</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
+        <v>126</v>
+      </c>
+      <c r="I82" t="s">
+        <v>24</v>
       </c>
       <c r="J82" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K82" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L82">
-        <v>470</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
+        <v>4375</v>
+      </c>
+      <c r="M82" t="s">
+        <v>24</v>
+      </c>
+      <c r="N82" t="s">
+        <v>24</v>
       </c>
       <c r="O82" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P82" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5803,16 +5803,16 @@
         <v>16</v>
       </c>
       <c r="B83" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C83" t="s">
-        <v>221</v>
+        <v>50</v>
       </c>
       <c r="D83" t="s">
         <v>222</v>
       </c>
       <c r="E83" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F83" t="s">
         <v>35</v>
@@ -5823,29 +5823,29 @@
       <c r="H83" t="s">
         <v>23</v>
       </c>
-      <c r="I83">
-        <v>0</v>
+      <c r="I83" t="s">
+        <v>24</v>
       </c>
       <c r="J83" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K83" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L83">
-        <v>2140</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-      <c r="N83">
-        <v>0</v>
+        <v>20418</v>
+      </c>
+      <c r="M83" t="s">
+        <v>24</v>
+      </c>
+      <c r="N83" t="s">
+        <v>24</v>
       </c>
       <c r="O83" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P83" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5856,13 +5856,13 @@
         <v>223</v>
       </c>
       <c r="C84" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D84" t="s">
         <v>224</v>
       </c>
       <c r="E84" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F84" t="s">
         <v>35</v>
@@ -5873,29 +5873,29 @@
       <c r="H84" t="s">
         <v>23</v>
       </c>
-      <c r="I84">
-        <v>0</v>
+      <c r="I84" t="s">
+        <v>24</v>
       </c>
       <c r="J84" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L84">
-        <v>17749</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
+        <v>5014</v>
+      </c>
+      <c r="M84" t="s">
+        <v>24</v>
+      </c>
+      <c r="N84" t="s">
+        <v>24</v>
       </c>
       <c r="O84" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P84" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
